--- a/backend/data/tickets.xlsx
+++ b/backend/data/tickets.xlsx
@@ -544,6 +544,9 @@
       <c r="J4">
         <v>3</v>
       </c>
+      <c r="K4" t="str">
+        <v>15/04/2026</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
